--- a/data/trans_orig/P1805_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1805_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>39156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>658326</t>
+          <t>659066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671141</t>
+          <t>670997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642417</t>
+          <t>643534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661811</t>
+          <t>661681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1308286</t>
+          <t>1308483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1329990</t>
+          <t>1329935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>23582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39054</t>
+          <t>37388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68626</t>
+          <t>66546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>996263</t>
+          <t>995430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012446</t>
+          <t>1012256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>993876</t>
+          <t>994170</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018947</t>
+          <t>1019331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1996718</t>
+          <t>1998798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026290</t>
+          <t>2027956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34712</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45791</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740872</t>
+          <t>741041</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754260</t>
+          <t>753688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>750299</t>
+          <t>749647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770079</t>
+          <t>770444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1498772</t>
+          <t>1498290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1521278</t>
+          <t>1520867</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>37020</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41503</t>
+          <t>41020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72199</t>
+          <t>71945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63331</t>
+          <t>64384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98988</t>
+          <t>100888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900543</t>
+          <t>900547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921131</t>
+          <t>921031</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>971580</t>
+          <t>971834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1002276</t>
+          <t>1002759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1882358</t>
+          <t>1880458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1918015</t>
+          <t>1916962</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>78455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110010</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160910</t>
+          <t>155830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167506</t>
+          <t>164728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223618</t>
+          <t>223541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3316896</t>
+          <t>3315895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3346705</t>
+          <t>3347166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3383632</t>
+          <t>3388712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3434532</t>
+          <t>3435679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6715274</t>
+          <t>6715351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6771386</t>
+          <t>6774164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26879</t>
+          <t>28855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17342</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>25768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33242</t>
+          <t>36757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>619541</t>
+          <t>673127</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>608562</t>
+          <t>661855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>626322</t>
+          <t>680912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>658410</t>
+          <t>713938</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>651488</t>
+          <t>707345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663981</t>
+          <t>719873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1277952</t>
+          <t>1387066</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1265469</t>
+          <t>1373231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1286732</t>
+          <t>1397343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>37952</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26288</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46476</t>
+          <t>50579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>61952</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>49149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>79379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1171410</t>
+          <t>1024917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1157069</t>
+          <t>1010761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1183147</t>
+          <t>1034603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>922642</t>
+          <t>1032886</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>911630</t>
+          <t>1020259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931818</t>
+          <t>1042265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2094053</t>
+          <t>2057803</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2076397</t>
+          <t>2040376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2112879</t>
+          <t>2070606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>29116</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>45748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>42065</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17900</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57583</t>
+          <t>56855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65396</t>
+          <t>71181</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41590</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87441</t>
+          <t>92668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>678026</t>
+          <t>773957</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658941</t>
+          <t>757325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>688706</t>
+          <t>785137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>894058</t>
+          <t>769598</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>875217</t>
+          <t>754808</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>914900</t>
+          <t>781040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1572084</t>
+          <t>1543555</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1550039</t>
+          <t>1522068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1595890</t>
+          <t>1560826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637480</t>
+          <t>1614736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46916</t>
+          <t>46466</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3712,22 +3712,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66624</t>
+          <t>63797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>58001</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68898</t>
+          <t>73730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>104468</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>86372</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122890</t>
+          <t>128457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879915</t>
+          <t>943596</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860207</t>
+          <t>926265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>893064</t>
+          <t>956295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1040992</t>
+          <t>1060356</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025356</t>
+          <t>1044627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1054774</t>
+          <t>1072914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1920907</t>
+          <t>2003951</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1898195</t>
+          <t>1979962</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941345</t>
+          <t>2022047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>92163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170710</t>
+          <t>181297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220482</t>
+          <t>240328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>297091</t>
+          <t>309782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3348893</t>
+          <t>3415597</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3318141</t>
+          <t>3388529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3376342</t>
+          <t>3440599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3516103</t>
+          <t>3576778</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3490203</t>
+          <t>3552673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3546515</t>
+          <t>3598818</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6864996</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6823639</t>
+          <t>6956950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6900248</t>
+          <t>7026404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
